--- a/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-patient-ins.xlsx
+++ b/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T15:13:06+00:00</t>
+    <t>2026-02-18T10:14:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1224,7 +1224,7 @@
     <t>Patient.extension:TDDUIHouseholdSituation.extension:householdComposition.value[x]:valueCodeableConcept</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J385-composition-foyer-ms/FHIR/JDV-J385-composition-foyer-ms</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j385-composition-foyer-ms</t>
   </si>
   <si>
     <t>Patient.extension:TDDUIHouseholdSituation.extension:householdCompositionDescription</t>

--- a/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-patient-ins.xlsx
+++ b/416-contenu-fhir---mise-à-jour-de-lusager/ig/StructureDefinition-tddui-patient-ins.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10447" uniqueCount="1105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10447" uniqueCount="1104">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T10:14:45+00:00</t>
+    <t>2026-02-24T10:54:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -698,7 +698,7 @@
     <t>Carries the death place of the patient |Précise le lieu de décès du patient (hôpital, sur la voie publique, au domicile, etc.).</t>
   </si>
   <si>
-    <t>paysDeces</t>
+    <t>communeDeces/departementDeces/paysDeces</t>
   </si>
   <si>
     <t>Patient.extension:birthdateUpdateIndicator</t>
@@ -1644,7 +1644,7 @@
     <t>Hospital assigned patient identifier | IPP; Dans le cadre de ce volet, représente l'Identifiant local de l’usager au sein de la structure.</t>
   </si>
   <si>
-    <t>identifiantLocalUsagerESSMS</t>
+    <t>identifiantUsagerESSMS</t>
   </si>
   <si>
     <t>Patient.identifier:PI.id</t>
@@ -2706,9 +2706,6 @@
   </si>
   <si>
     <t>Patient.address.id</t>
-  </si>
-  <si>
-    <t>idAdresse</t>
   </si>
   <si>
     <t>Patient.address.extension</t>
@@ -3848,7 +3845,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="30.4765625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="38.2578125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="134.453125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="34.98828125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
@@ -29532,7 +29529,7 @@
         <v>82</v>
       </c>
       <c r="AK214" t="s" s="2">
-        <v>853</v>
+        <v>82</v>
       </c>
       <c r="AL214" t="s" s="2">
         <v>109</v>
@@ -29552,10 +29549,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -29672,10 +29669,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C216" t="s" s="2">
         <v>254</v>
@@ -29792,10 +29789,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C217" t="s" s="2">
         <v>400</v>
@@ -29912,10 +29909,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -30034,10 +30031,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -30134,7 +30131,7 @@
         <v>103</v>
       </c>
       <c r="AK219" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AL219" t="s" s="2">
         <v>269</v>
@@ -30154,10 +30151,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -30276,10 +30273,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -30394,10 +30391,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -30423,10 +30420,10 @@
         <v>105</v>
       </c>
       <c r="L222" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="M222" t="s" s="2">
         <v>863</v>
-      </c>
-      <c r="M222" t="s" s="2">
-        <v>864</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" s="2"/>
@@ -30512,10 +30509,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -30628,13 +30625,13 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="B224" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="C224" t="s" s="2">
         <v>866</v>
-      </c>
-      <c r="B224" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="C224" t="s" s="2">
-        <v>867</v>
       </c>
       <c r="D224" t="s" s="2">
         <v>82</v>
@@ -30656,13 +30653,13 @@
         <v>82</v>
       </c>
       <c r="K224" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="L224" t="s" s="2">
         <v>868</v>
       </c>
-      <c r="L224" t="s" s="2">
+      <c r="M224" t="s" s="2">
         <v>869</v>
-      </c>
-      <c r="M224" t="s" s="2">
-        <v>870</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -30731,7 +30728,7 @@
         <v>82</v>
       </c>
       <c r="AL224" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AM224" t="s" s="2">
         <v>82</v>
@@ -30748,13 +30745,13 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="C225" t="s" s="2">
         <v>872</v>
-      </c>
-      <c r="B225" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="C225" t="s" s="2">
-        <v>873</v>
       </c>
       <c r="D225" t="s" s="2">
         <v>82</v>
@@ -30776,13 +30773,13 @@
         <v>82</v>
       </c>
       <c r="K225" t="s" s="2">
+        <v>873</v>
+      </c>
+      <c r="L225" t="s" s="2">
+        <v>872</v>
+      </c>
+      <c r="M225" t="s" s="2">
         <v>874</v>
-      </c>
-      <c r="L225" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="M225" t="s" s="2">
-        <v>875</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -30848,10 +30845,10 @@
         <v>120</v>
       </c>
       <c r="AK225" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="AL225" t="s" s="2">
         <v>876</v>
-      </c>
-      <c r="AL225" t="s" s="2">
-        <v>877</v>
       </c>
       <c r="AM225" t="s" s="2">
         <v>82</v>
@@ -30868,13 +30865,13 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="C226" t="s" s="2">
         <v>878</v>
-      </c>
-      <c r="B226" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="C226" t="s" s="2">
-        <v>879</v>
       </c>
       <c r="D226" t="s" s="2">
         <v>82</v>
@@ -30896,13 +30893,13 @@
         <v>82</v>
       </c>
       <c r="K226" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="L226" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="M226" t="s" s="2">
         <v>880</v>
-      </c>
-      <c r="L226" t="s" s="2">
-        <v>879</v>
-      </c>
-      <c r="M226" t="s" s="2">
-        <v>881</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -30968,10 +30965,10 @@
         <v>120</v>
       </c>
       <c r="AK226" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="AL226" t="s" s="2">
         <v>882</v>
-      </c>
-      <c r="AL226" t="s" s="2">
-        <v>883</v>
       </c>
       <c r="AM226" t="s" s="2">
         <v>82</v>
@@ -30988,13 +30985,13 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
+        <v>883</v>
+      </c>
+      <c r="B227" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="C227" t="s" s="2">
         <v>884</v>
-      </c>
-      <c r="B227" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="C227" t="s" s="2">
-        <v>885</v>
       </c>
       <c r="D227" t="s" s="2">
         <v>82</v>
@@ -31016,13 +31013,13 @@
         <v>82</v>
       </c>
       <c r="K227" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="L227" t="s" s="2">
         <v>886</v>
       </c>
-      <c r="L227" t="s" s="2">
+      <c r="M227" t="s" s="2">
         <v>887</v>
-      </c>
-      <c r="M227" t="s" s="2">
-        <v>888</v>
       </c>
       <c r="N227" s="2"/>
       <c r="O227" s="2"/>
@@ -31091,7 +31088,7 @@
         <v>82</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>82</v>
@@ -31108,13 +31105,13 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="B228" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="C228" t="s" s="2">
         <v>890</v>
-      </c>
-      <c r="B228" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="C228" t="s" s="2">
-        <v>891</v>
       </c>
       <c r="D228" t="s" s="2">
         <v>82</v>
@@ -31136,13 +31133,13 @@
         <v>82</v>
       </c>
       <c r="K228" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="L228" t="s" s="2">
         <v>892</v>
       </c>
-      <c r="L228" t="s" s="2">
+      <c r="M228" t="s" s="2">
         <v>893</v>
-      </c>
-      <c r="M228" t="s" s="2">
-        <v>894</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -31211,7 +31208,7 @@
         <v>82</v>
       </c>
       <c r="AL228" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="AM228" t="s" s="2">
         <v>82</v>
@@ -31228,10 +31225,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="B229" t="s" s="2">
         <v>896</v>
-      </c>
-      <c r="B229" t="s" s="2">
-        <v>897</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -31346,10 +31343,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="B230" t="s" s="2">
         <v>898</v>
-      </c>
-      <c r="B230" t="s" s="2">
-        <v>899</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -31464,10 +31461,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="B231" t="s" s="2">
         <v>900</v>
-      </c>
-      <c r="B231" t="s" s="2">
-        <v>901</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -31507,7 +31504,7 @@
       </c>
       <c r="Q231" s="2"/>
       <c r="R231" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="S231" t="s" s="2">
         <v>82</v>
@@ -31584,10 +31581,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
+        <v>902</v>
+      </c>
+      <c r="B232" t="s" s="2">
         <v>903</v>
-      </c>
-      <c r="B232" t="s" s="2">
-        <v>904</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -31616,7 +31613,7 @@
         <v>373</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
@@ -31647,7 +31644,7 @@
       </c>
       <c r="Y232" s="2"/>
       <c r="Z232" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>82</v>
@@ -31674,7 +31671,7 @@
         <v>91</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>103</v>
@@ -31700,13 +31697,13 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="C233" t="s" s="2">
         <v>908</v>
-      </c>
-      <c r="B233" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="C233" t="s" s="2">
-        <v>909</v>
       </c>
       <c r="D233" t="s" s="2">
         <v>82</v>
@@ -31728,13 +31725,13 @@
         <v>82</v>
       </c>
       <c r="K233" t="s" s="2">
+        <v>909</v>
+      </c>
+      <c r="L233" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="M233" t="s" s="2">
         <v>910</v>
-      </c>
-      <c r="L233" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="M233" t="s" s="2">
-        <v>911</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" s="2"/>
@@ -31800,10 +31797,10 @@
         <v>120</v>
       </c>
       <c r="AK233" t="s" s="2">
+        <v>911</v>
+      </c>
+      <c r="AL233" t="s" s="2">
         <v>912</v>
-      </c>
-      <c r="AL233" t="s" s="2">
-        <v>913</v>
       </c>
       <c r="AM233" t="s" s="2">
         <v>82</v>
@@ -31820,13 +31817,13 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
+        <v>913</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="C234" t="s" s="2">
         <v>914</v>
-      </c>
-      <c r="B234" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="C234" t="s" s="2">
-        <v>915</v>
       </c>
       <c r="D234" t="s" s="2">
         <v>82</v>
@@ -31848,13 +31845,13 @@
         <v>82</v>
       </c>
       <c r="K234" t="s" s="2">
+        <v>915</v>
+      </c>
+      <c r="L234" t="s" s="2">
+        <v>914</v>
+      </c>
+      <c r="M234" t="s" s="2">
         <v>916</v>
-      </c>
-      <c r="L234" t="s" s="2">
-        <v>915</v>
-      </c>
-      <c r="M234" t="s" s="2">
-        <v>917</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -31920,10 +31917,10 @@
         <v>120</v>
       </c>
       <c r="AK234" t="s" s="2">
+        <v>917</v>
+      </c>
+      <c r="AL234" t="s" s="2">
         <v>918</v>
-      </c>
-      <c r="AL234" t="s" s="2">
-        <v>919</v>
       </c>
       <c r="AM234" t="s" s="2">
         <v>82</v>
@@ -31940,13 +31937,13 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
+        <v>919</v>
+      </c>
+      <c r="B235" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="C235" t="s" s="2">
         <v>920</v>
-      </c>
-      <c r="B235" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="C235" t="s" s="2">
-        <v>921</v>
       </c>
       <c r="D235" t="s" s="2">
         <v>82</v>
@@ -31968,13 +31965,13 @@
         <v>82</v>
       </c>
       <c r="K235" t="s" s="2">
+        <v>921</v>
+      </c>
+      <c r="L235" t="s" s="2">
         <v>922</v>
       </c>
-      <c r="L235" t="s" s="2">
+      <c r="M235" t="s" s="2">
         <v>923</v>
-      </c>
-      <c r="M235" t="s" s="2">
-        <v>924</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" s="2"/>
@@ -32060,10 +32057,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -32089,10 +32086,10 @@
         <v>105</v>
       </c>
       <c r="L236" t="s" s="2">
+        <v>925</v>
+      </c>
+      <c r="M236" t="s" s="2">
         <v>926</v>
-      </c>
-      <c r="M236" t="s" s="2">
-        <v>927</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
@@ -32116,34 +32113,34 @@
         <v>82</v>
       </c>
       <c r="W236" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="X236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF236" t="s" s="2">
         <v>928</v>
-      </c>
-      <c r="X236" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y236" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z236" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA236" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB236" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC236" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD236" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE236" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF236" t="s" s="2">
-        <v>929</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>80</v>
@@ -32178,10 +32175,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -32296,10 +32293,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -32414,10 +32411,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -32512,7 +32509,7 @@
         <v>103</v>
       </c>
       <c r="AK239" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="AL239" t="s" s="2">
         <v>325</v>
@@ -32532,10 +32529,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -32630,7 +32627,7 @@
         <v>103</v>
       </c>
       <c r="AK240" t="s" s="2">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="AL240" t="s" s="2">
         <v>334</v>
@@ -32650,10 +32647,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -32715,7 +32712,7 @@
       </c>
       <c r="Y241" s="2"/>
       <c r="Z241" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="AA241" t="s" s="2">
         <v>82</v>
@@ -32748,7 +32745,7 @@
         <v>103</v>
       </c>
       <c r="AK241" t="s" s="2">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AL241" t="s" s="2">
         <v>342</v>
@@ -32768,10 +32765,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -32888,10 +32885,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -32917,14 +32914,14 @@
         <v>378</v>
       </c>
       <c r="L243" t="s" s="2">
+        <v>940</v>
+      </c>
+      <c r="M243" t="s" s="2">
         <v>941</v>
-      </c>
-      <c r="M243" t="s" s="2">
-        <v>942</v>
       </c>
       <c r="N243" s="2"/>
       <c r="O243" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="P243" t="s" s="2">
         <v>82</v>
@@ -32953,7 +32950,7 @@
       </c>
       <c r="Y243" s="2"/>
       <c r="Z243" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="AA243" t="s" s="2">
         <v>82</v>
@@ -32971,7 +32968,7 @@
         <v>82</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>80</v>
@@ -32989,16 +32986,16 @@
         <v>82</v>
       </c>
       <c r="AL243" t="s" s="2">
+        <v>944</v>
+      </c>
+      <c r="AM243" t="s" s="2">
         <v>945</v>
       </c>
-      <c r="AM243" t="s" s="2">
+      <c r="AN243" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO243" t="s" s="2">
         <v>946</v>
-      </c>
-      <c r="AN243" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO243" t="s" s="2">
-        <v>947</v>
       </c>
       <c r="AP243" t="s" s="2">
         <v>82</v>
@@ -33006,10 +33003,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -33032,19 +33029,19 @@
         <v>82</v>
       </c>
       <c r="K244" t="s" s="2">
+        <v>948</v>
+      </c>
+      <c r="L244" t="s" s="2">
         <v>949</v>
       </c>
-      <c r="L244" t="s" s="2">
+      <c r="M244" t="s" s="2">
         <v>950</v>
       </c>
-      <c r="M244" t="s" s="2">
+      <c r="N244" t="s" s="2">
         <v>951</v>
       </c>
-      <c r="N244" t="s" s="2">
+      <c r="O244" t="s" s="2">
         <v>952</v>
-      </c>
-      <c r="O244" t="s" s="2">
-        <v>953</v>
       </c>
       <c r="P244" t="s" s="2">
         <v>82</v>
@@ -33093,7 +33090,7 @@
         <v>82</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>80</v>
@@ -33111,7 +33108,7 @@
         <v>82</v>
       </c>
       <c r="AL244" t="s" s="2">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="AM244" t="s" s="2">
         <v>109</v>
@@ -33120,7 +33117,7 @@
         <v>82</v>
       </c>
       <c r="AO244" t="s" s="2">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AP244" t="s" s="2">
         <v>82</v>
@@ -33128,10 +33125,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -33154,19 +33151,19 @@
         <v>82</v>
       </c>
       <c r="K245" t="s" s="2">
+        <v>956</v>
+      </c>
+      <c r="L245" t="s" s="2">
         <v>957</v>
       </c>
-      <c r="L245" t="s" s="2">
+      <c r="M245" t="s" s="2">
         <v>958</v>
       </c>
-      <c r="M245" t="s" s="2">
+      <c r="N245" t="s" s="2">
         <v>959</v>
       </c>
-      <c r="N245" t="s" s="2">
+      <c r="O245" t="s" s="2">
         <v>960</v>
-      </c>
-      <c r="O245" t="s" s="2">
-        <v>961</v>
       </c>
       <c r="P245" t="s" s="2">
         <v>82</v>
@@ -33215,7 +33212,7 @@
         <v>82</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>80</v>
@@ -33230,10 +33227,10 @@
         <v>103</v>
       </c>
       <c r="AK245" t="s" s="2">
+        <v>961</v>
+      </c>
+      <c r="AL245" t="s" s="2">
         <v>962</v>
-      </c>
-      <c r="AL245" t="s" s="2">
-        <v>963</v>
       </c>
       <c r="AM245" t="s" s="2">
         <v>109</v>
@@ -33242,7 +33239,7 @@
         <v>82</v>
       </c>
       <c r="AO245" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="AP245" t="s" s="2">
         <v>82</v>
@@ -33250,10 +33247,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -33276,19 +33273,19 @@
         <v>82</v>
       </c>
       <c r="K246" t="s" s="2">
+        <v>965</v>
+      </c>
+      <c r="L246" t="s" s="2">
         <v>966</v>
       </c>
-      <c r="L246" t="s" s="2">
+      <c r="M246" t="s" s="2">
         <v>967</v>
       </c>
-      <c r="M246" t="s" s="2">
+      <c r="N246" t="s" s="2">
         <v>968</v>
       </c>
-      <c r="N246" t="s" s="2">
+      <c r="O246" t="s" s="2">
         <v>969</v>
-      </c>
-      <c r="O246" t="s" s="2">
-        <v>970</v>
       </c>
       <c r="P246" t="s" s="2">
         <v>82</v>
@@ -33337,7 +33334,7 @@
         <v>82</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>80</v>
@@ -33349,13 +33346,13 @@
         <v>82</v>
       </c>
       <c r="AJ246" t="s" s="2">
+        <v>970</v>
+      </c>
+      <c r="AK246" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL246" t="s" s="2">
         <v>971</v>
-      </c>
-      <c r="AK246" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL246" t="s" s="2">
-        <v>972</v>
       </c>
       <c r="AM246" t="s" s="2">
         <v>109</v>
@@ -33372,10 +33369,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -33490,10 +33487,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -33606,13 +33603,13 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
+        <v>974</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>973</v>
+      </c>
+      <c r="C249" t="s" s="2">
         <v>975</v>
-      </c>
-      <c r="B249" t="s" s="2">
-        <v>974</v>
-      </c>
-      <c r="C249" t="s" s="2">
-        <v>976</v>
       </c>
       <c r="D249" t="s" s="2">
         <v>82</v>
@@ -33634,13 +33631,13 @@
         <v>82</v>
       </c>
       <c r="K249" t="s" s="2">
+        <v>976</v>
+      </c>
+      <c r="L249" t="s" s="2">
         <v>977</v>
       </c>
-      <c r="L249" t="s" s="2">
+      <c r="M249" t="s" s="2">
         <v>978</v>
-      </c>
-      <c r="M249" t="s" s="2">
-        <v>979</v>
       </c>
       <c r="N249" s="2"/>
       <c r="O249" s="2"/>
@@ -33726,13 +33723,13 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
+        <v>979</v>
+      </c>
+      <c r="B250" t="s" s="2">
+        <v>973</v>
+      </c>
+      <c r="C250" t="s" s="2">
         <v>980</v>
-      </c>
-      <c r="B250" t="s" s="2">
-        <v>974</v>
-      </c>
-      <c r="C250" t="s" s="2">
-        <v>981</v>
       </c>
       <c r="D250" t="s" s="2">
         <v>82</v>
@@ -33754,13 +33751,13 @@
         <v>82</v>
       </c>
       <c r="K250" t="s" s="2">
+        <v>981</v>
+      </c>
+      <c r="L250" t="s" s="2">
         <v>982</v>
       </c>
-      <c r="L250" t="s" s="2">
+      <c r="M250" t="s" s="2">
         <v>983</v>
-      </c>
-      <c r="M250" t="s" s="2">
-        <v>984</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" s="2"/>
@@ -33846,14 +33843,14 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E251" s="2"/>
       <c r="F251" t="s" s="2">
@@ -33875,10 +33872,10 @@
         <v>112</v>
       </c>
       <c r="L251" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="M251" t="s" s="2">
         <v>987</v>
-      </c>
-      <c r="M251" t="s" s="2">
-        <v>988</v>
       </c>
       <c r="N251" t="s" s="2">
         <v>115</v>
@@ -33933,7 +33930,7 @@
         <v>82</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>80</v>
@@ -33968,10 +33965,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -33997,14 +33994,14 @@
         <v>378</v>
       </c>
       <c r="L252" t="s" s="2">
+        <v>990</v>
+      </c>
+      <c r="M252" t="s" s="2">
         <v>991</v>
-      </c>
-      <c r="M252" t="s" s="2">
-        <v>992</v>
       </c>
       <c r="N252" s="2"/>
       <c r="O252" t="s" s="2">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="P252" t="s" s="2">
         <v>82</v>
@@ -34032,16 +34029,16 @@
         <v>154</v>
       </c>
       <c r="Y252" t="s" s="2">
+        <v>993</v>
+      </c>
+      <c r="Z252" t="s" s="2">
         <v>994</v>
       </c>
-      <c r="Z252" t="s" s="2">
+      <c r="AA252" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB252" t="s" s="2">
         <v>995</v>
-      </c>
-      <c r="AA252" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB252" t="s" s="2">
-        <v>996</v>
       </c>
       <c r="AC252" s="2"/>
       <c r="AD252" t="s" s="2">
@@ -34051,7 +34048,7 @@
         <v>118</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>80</v>
@@ -34069,7 +34066,7 @@
         <v>82</v>
       </c>
       <c r="AL252" t="s" s="2">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="AM252" t="s" s="2">
         <v>109</v>
@@ -34078,7 +34075,7 @@
         <v>82</v>
       </c>
       <c r="AO252" t="s" s="2">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AP252" t="s" s="2">
         <v>82</v>
@@ -34086,13 +34083,13 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
+        <v>998</v>
+      </c>
+      <c r="B253" t="s" s="2">
+        <v>989</v>
+      </c>
+      <c r="C253" t="s" s="2">
         <v>999</v>
-      </c>
-      <c r="B253" t="s" s="2">
-        <v>990</v>
-      </c>
-      <c r="C253" t="s" s="2">
-        <v>1000</v>
       </c>
       <c r="D253" t="s" s="2">
         <v>82</v>
@@ -34117,14 +34114,14 @@
         <v>378</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="N253" s="2"/>
       <c r="O253" t="s" s="2">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="P253" t="s" s="2">
         <v>82</v>
@@ -34153,7 +34150,7 @@
       </c>
       <c r="Y253" s="2"/>
       <c r="Z253" t="s" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="AA253" t="s" s="2">
         <v>82</v>
@@ -34171,7 +34168,7 @@
         <v>82</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>80</v>
@@ -34189,7 +34186,7 @@
         <v>82</v>
       </c>
       <c r="AL253" t="s" s="2">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="AM253" t="s" s="2">
         <v>109</v>
@@ -34198,7 +34195,7 @@
         <v>82</v>
       </c>
       <c r="AO253" t="s" s="2">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AP253" t="s" s="2">
         <v>82</v>
@@ -34206,13 +34203,13 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
+        <v>1002</v>
+      </c>
+      <c r="B254" t="s" s="2">
+        <v>989</v>
+      </c>
+      <c r="C254" t="s" s="2">
         <v>1003</v>
-      </c>
-      <c r="B254" t="s" s="2">
-        <v>990</v>
-      </c>
-      <c r="C254" t="s" s="2">
-        <v>1004</v>
       </c>
       <c r="D254" t="s" s="2">
         <v>82</v>
@@ -34237,14 +34234,14 @@
         <v>378</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="N254" s="2"/>
       <c r="O254" t="s" s="2">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="P254" t="s" s="2">
         <v>82</v>
@@ -34273,7 +34270,7 @@
       </c>
       <c r="Y254" s="2"/>
       <c r="Z254" t="s" s="2">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AA254" t="s" s="2">
         <v>82</v>
@@ -34291,7 +34288,7 @@
         <v>82</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>80</v>
@@ -34309,7 +34306,7 @@
         <v>82</v>
       </c>
       <c r="AL254" t="s" s="2">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="AM254" t="s" s="2">
         <v>109</v>
@@ -34318,7 +34315,7 @@
         <v>82</v>
       </c>
       <c r="AO254" t="s" s="2">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AP254" t="s" s="2">
         <v>82</v>
@@ -34326,10 +34323,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -34352,19 +34349,19 @@
         <v>82</v>
       </c>
       <c r="K255" t="s" s="2">
+        <v>1007</v>
+      </c>
+      <c r="L255" t="s" s="2">
         <v>1008</v>
       </c>
-      <c r="L255" t="s" s="2">
+      <c r="M255" t="s" s="2">
         <v>1009</v>
       </c>
-      <c r="M255" t="s" s="2">
+      <c r="N255" t="s" s="2">
         <v>1010</v>
       </c>
-      <c r="N255" t="s" s="2">
+      <c r="O255" t="s" s="2">
         <v>1011</v>
-      </c>
-      <c r="O255" t="s" s="2">
-        <v>1012</v>
       </c>
       <c r="P255" t="s" s="2">
         <v>82</v>
@@ -34413,7 +34410,7 @@
         <v>82</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>80</v>
@@ -34431,16 +34428,16 @@
         <v>82</v>
       </c>
       <c r="AL255" t="s" s="2">
+        <v>1012</v>
+      </c>
+      <c r="AM255" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN255" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO255" t="s" s="2">
         <v>1013</v>
-      </c>
-      <c r="AM255" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN255" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO255" t="s" s="2">
-        <v>1014</v>
       </c>
       <c r="AP255" t="s" s="2">
         <v>82</v>
@@ -34448,10 +34445,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -34483,7 +34480,7 @@
         <v>764</v>
       </c>
       <c r="N256" t="s" s="2">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="O256" t="s" s="2">
         <v>766</v>
@@ -34535,7 +34532,7 @@
         <v>82</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>80</v>
@@ -34570,10 +34567,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -34596,17 +34593,17 @@
         <v>82</v>
       </c>
       <c r="K257" t="s" s="2">
+        <v>1017</v>
+      </c>
+      <c r="L257" t="s" s="2">
         <v>1018</v>
       </c>
-      <c r="L257" t="s" s="2">
+      <c r="M257" t="s" s="2">
         <v>1019</v>
-      </c>
-      <c r="M257" t="s" s="2">
-        <v>1020</v>
       </c>
       <c r="N257" s="2"/>
       <c r="O257" t="s" s="2">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="P257" t="s" s="2">
         <v>82</v>
@@ -34655,7 +34652,7 @@
         <v>82</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>80</v>
@@ -34673,7 +34670,7 @@
         <v>82</v>
       </c>
       <c r="AL257" t="s" s="2">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AM257" t="s" s="2">
         <v>109</v>
@@ -34682,7 +34679,7 @@
         <v>82</v>
       </c>
       <c r="AO257" t="s" s="2">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AP257" t="s" s="2">
         <v>82</v>
@@ -34690,10 +34687,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -34719,14 +34716,14 @@
         <v>172</v>
       </c>
       <c r="L258" t="s" s="2">
+        <v>1024</v>
+      </c>
+      <c r="M258" t="s" s="2">
         <v>1025</v>
-      </c>
-      <c r="M258" t="s" s="2">
-        <v>1026</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" t="s" s="2">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>82</v>
@@ -34754,11 +34751,11 @@
         <v>265</v>
       </c>
       <c r="Y258" t="s" s="2">
+        <v>1027</v>
+      </c>
+      <c r="Z258" t="s" s="2">
         <v>1028</v>
       </c>
-      <c r="Z258" t="s" s="2">
-        <v>1029</v>
-      </c>
       <c r="AA258" t="s" s="2">
         <v>82</v>
       </c>
@@ -34775,7 +34772,7 @@
         <v>82</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>80</v>
@@ -34802,7 +34799,7 @@
         <v>82</v>
       </c>
       <c r="AO258" t="s" s="2">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="AP258" t="s" s="2">
         <v>82</v>
@@ -34810,10 +34807,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -34839,14 +34836,14 @@
         <v>488</v>
       </c>
       <c r="L259" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="M259" t="s" s="2">
         <v>1032</v>
-      </c>
-      <c r="M259" t="s" s="2">
-        <v>1033</v>
       </c>
       <c r="N259" s="2"/>
       <c r="O259" t="s" s="2">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="P259" t="s" s="2">
         <v>82</v>
@@ -34895,7 +34892,7 @@
         <v>82</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>80</v>
@@ -34904,7 +34901,7 @@
         <v>91</v>
       </c>
       <c r="AI259" t="s" s="2">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="AJ259" t="s" s="2">
         <v>103</v>
@@ -34913,7 +34910,7 @@
         <v>82</v>
       </c>
       <c r="AL259" t="s" s="2">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="AM259" t="s" s="2">
         <v>109</v>
@@ -34922,7 +34919,7 @@
         <v>82</v>
       </c>
       <c r="AO259" t="s" s="2">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="AP259" t="s" s="2">
         <v>82</v>
@@ -34930,10 +34927,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -34959,10 +34956,10 @@
         <v>346</v>
       </c>
       <c r="L260" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="M260" t="s" s="2">
         <v>1039</v>
-      </c>
-      <c r="M260" t="s" s="2">
-        <v>1040</v>
       </c>
       <c r="N260" s="2"/>
       <c r="O260" s="2"/>
@@ -35013,7 +35010,7 @@
         <v>82</v>
       </c>
       <c r="AF260" t="s" s="2">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="AG260" t="s" s="2">
         <v>80</v>
@@ -35031,7 +35028,7 @@
         <v>82</v>
       </c>
       <c r="AL260" t="s" s="2">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="AM260" t="s" s="2">
         <v>109</v>
@@ -35048,10 +35045,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -35074,19 +35071,19 @@
         <v>82</v>
       </c>
       <c r="K261" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L261" t="s" s="2">
+        <v>1042</v>
+      </c>
+      <c r="M261" t="s" s="2">
         <v>1043</v>
       </c>
-      <c r="M261" t="s" s="2">
+      <c r="N261" t="s" s="2">
         <v>1044</v>
       </c>
-      <c r="N261" t="s" s="2">
+      <c r="O261" t="s" s="2">
         <v>1045</v>
-      </c>
-      <c r="O261" t="s" s="2">
-        <v>1046</v>
       </c>
       <c r="P261" t="s" s="2">
         <v>82</v>
@@ -35135,7 +35132,7 @@
         <v>82</v>
       </c>
       <c r="AF261" t="s" s="2">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="AG261" t="s" s="2">
         <v>80</v>
@@ -35153,10 +35150,10 @@
         <v>82</v>
       </c>
       <c r="AL261" t="s" s="2">
+        <v>1046</v>
+      </c>
+      <c r="AM261" t="s" s="2">
         <v>1047</v>
-      </c>
-      <c r="AM261" t="s" s="2">
-        <v>1048</v>
       </c>
       <c r="AN261" t="s" s="2">
         <v>82</v>
@@ -35170,10 +35167,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -35288,10 +35285,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -35408,14 +35405,14 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E264" s="2"/>
       <c r="F264" t="s" s="2">
@@ -35437,10 +35434,10 @@
         <v>112</v>
       </c>
       <c r="L264" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="M264" t="s" s="2">
         <v>987</v>
-      </c>
-      <c r="M264" t="s" s="2">
-        <v>988</v>
       </c>
       <c r="N264" t="s" s="2">
         <v>115</v>
@@ -35495,7 +35492,7 @@
         <v>82</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>80</v>
@@ -35530,10 +35527,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -35559,16 +35556,16 @@
         <v>378</v>
       </c>
       <c r="L265" t="s" s="2">
+        <v>1052</v>
+      </c>
+      <c r="M265" t="s" s="2">
         <v>1053</v>
       </c>
-      <c r="M265" t="s" s="2">
+      <c r="N265" t="s" s="2">
         <v>1054</v>
       </c>
-      <c r="N265" t="s" s="2">
+      <c r="O265" t="s" s="2">
         <v>1055</v>
-      </c>
-      <c r="O265" t="s" s="2">
-        <v>1056</v>
       </c>
       <c r="P265" t="s" s="2">
         <v>82</v>
@@ -35597,7 +35594,7 @@
       </c>
       <c r="Y265" s="2"/>
       <c r="Z265" t="s" s="2">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="AA265" t="s" s="2">
         <v>82</v>
@@ -35615,7 +35612,7 @@
         <v>82</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>91</v>
@@ -35630,19 +35627,19 @@
         <v>103</v>
       </c>
       <c r="AK265" t="s" s="2">
+        <v>1057</v>
+      </c>
+      <c r="AL265" t="s" s="2">
         <v>1058</v>
       </c>
-      <c r="AL265" t="s" s="2">
+      <c r="AM265" t="s" s="2">
         <v>1059</v>
       </c>
-      <c r="AM265" t="s" s="2">
+      <c r="AN265" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO265" t="s" s="2">
         <v>1060</v>
-      </c>
-      <c r="AN265" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO265" t="s" s="2">
-        <v>1061</v>
       </c>
       <c r="AP265" t="s" s="2">
         <v>82</v>
@@ -35650,10 +35647,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -35679,16 +35676,16 @@
         <v>654</v>
       </c>
       <c r="L266" t="s" s="2">
+        <v>1062</v>
+      </c>
+      <c r="M266" t="s" s="2">
         <v>1063</v>
       </c>
-      <c r="M266" t="s" s="2">
+      <c r="N266" t="s" s="2">
         <v>1064</v>
       </c>
-      <c r="N266" t="s" s="2">
+      <c r="O266" t="s" s="2">
         <v>1065</v>
-      </c>
-      <c r="O266" t="s" s="2">
-        <v>1066</v>
       </c>
       <c r="P266" t="s" s="2">
         <v>82</v>
@@ -35737,7 +35734,7 @@
         <v>82</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>80</v>
@@ -35755,16 +35752,16 @@
         <v>82</v>
       </c>
       <c r="AL266" t="s" s="2">
+        <v>1066</v>
+      </c>
+      <c r="AM266" t="s" s="2">
         <v>1067</v>
       </c>
-      <c r="AM266" t="s" s="2">
+      <c r="AN266" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO266" t="s" s="2">
         <v>1068</v>
-      </c>
-      <c r="AN266" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO266" t="s" s="2">
-        <v>1069</v>
       </c>
       <c r="AP266" t="s" s="2">
         <v>82</v>
@@ -35772,14 +35769,14 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="E267" s="2"/>
       <c r="F267" t="s" s="2">
@@ -35798,16 +35795,16 @@
         <v>82</v>
       </c>
       <c r="K267" t="s" s="2">
+        <v>1071</v>
+      </c>
+      <c r="L267" t="s" s="2">
         <v>1072</v>
       </c>
-      <c r="L267" t="s" s="2">
+      <c r="M267" t="s" s="2">
         <v>1073</v>
       </c>
-      <c r="M267" t="s" s="2">
+      <c r="N267" t="s" s="2">
         <v>1074</v>
-      </c>
-      <c r="N267" t="s" s="2">
-        <v>1075</v>
       </c>
       <c r="O267" s="2"/>
       <c r="P267" t="s" s="2">
@@ -35857,7 +35854,7 @@
         <v>82</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>80</v>
@@ -35875,7 +35872,7 @@
         <v>82</v>
       </c>
       <c r="AL267" t="s" s="2">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="AM267" t="s" s="2">
         <v>109</v>
@@ -35884,7 +35881,7 @@
         <v>82</v>
       </c>
       <c r="AO267" t="s" s="2">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AP267" t="s" s="2">
         <v>82</v>
@@ -35892,10 +35889,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -35918,19 +35915,19 @@
         <v>92</v>
       </c>
       <c r="K268" t="s" s="2">
+        <v>1078</v>
+      </c>
+      <c r="L268" t="s" s="2">
         <v>1079</v>
       </c>
-      <c r="L268" t="s" s="2">
+      <c r="M268" t="s" s="2">
         <v>1080</v>
       </c>
-      <c r="M268" t="s" s="2">
+      <c r="N268" t="s" s="2">
         <v>1081</v>
       </c>
-      <c r="N268" t="s" s="2">
+      <c r="O268" t="s" s="2">
         <v>1082</v>
-      </c>
-      <c r="O268" t="s" s="2">
-        <v>1083</v>
       </c>
       <c r="P268" t="s" s="2">
         <v>82</v>
@@ -35979,7 +35976,7 @@
         <v>82</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>80</v>
@@ -35997,10 +35994,10 @@
         <v>82</v>
       </c>
       <c r="AL268" t="s" s="2">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="AM268" t="s" s="2">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="AN268" t="s" s="2">
         <v>82</v>
@@ -36014,10 +36011,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -36040,19 +36037,19 @@
         <v>92</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L269" t="s" s="2">
+        <v>1085</v>
+      </c>
+      <c r="M269" t="s" s="2">
         <v>1086</v>
       </c>
-      <c r="M269" t="s" s="2">
+      <c r="N269" t="s" s="2">
         <v>1087</v>
       </c>
-      <c r="N269" t="s" s="2">
+      <c r="O269" t="s" s="2">
         <v>1088</v>
-      </c>
-      <c r="O269" t="s" s="2">
-        <v>1089</v>
       </c>
       <c r="P269" t="s" s="2">
         <v>82</v>
@@ -36101,7 +36098,7 @@
         <v>82</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>80</v>
@@ -36119,7 +36116,7 @@
         <v>82</v>
       </c>
       <c r="AL269" t="s" s="2">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="AM269" t="s" s="2">
         <v>109</v>
@@ -36136,10 +36133,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -36254,10 +36251,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -36374,14 +36371,14 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E272" s="2"/>
       <c r="F272" t="s" s="2">
@@ -36403,10 +36400,10 @@
         <v>112</v>
       </c>
       <c r="L272" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="M272" t="s" s="2">
         <v>987</v>
-      </c>
-      <c r="M272" t="s" s="2">
-        <v>988</v>
       </c>
       <c r="N272" t="s" s="2">
         <v>115</v>
@@ -36461,7 +36458,7 @@
         <v>82</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="AG272" t="s" s="2">
         <v>80</v>
@@ -36496,10 +36493,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -36522,16 +36519,16 @@
         <v>92</v>
       </c>
       <c r="K273" t="s" s="2">
+        <v>1094</v>
+      </c>
+      <c r="L273" t="s" s="2">
         <v>1095</v>
       </c>
-      <c r="L273" t="s" s="2">
+      <c r="M273" t="s" s="2">
         <v>1096</v>
       </c>
-      <c r="M273" t="s" s="2">
+      <c r="N273" t="s" s="2">
         <v>1097</v>
-      </c>
-      <c r="N273" t="s" s="2">
-        <v>1098</v>
       </c>
       <c r="O273" s="2"/>
       <c r="P273" t="s" s="2">
@@ -36581,7 +36578,7 @@
         <v>82</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>91</v>
@@ -36608,7 +36605,7 @@
         <v>82</v>
       </c>
       <c r="AO273" t="s" s="2">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="AP273" t="s" s="2">
         <v>82</v>
@@ -36616,10 +36613,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -36645,10 +36642,10 @@
         <v>172</v>
       </c>
       <c r="L274" t="s" s="2">
+        <v>1100</v>
+      </c>
+      <c r="M274" t="s" s="2">
         <v>1101</v>
-      </c>
-      <c r="M274" t="s" s="2">
-        <v>1102</v>
       </c>
       <c r="N274" s="2"/>
       <c r="O274" s="2"/>
@@ -36678,11 +36675,11 @@
         <v>265</v>
       </c>
       <c r="Y274" t="s" s="2">
+        <v>1101</v>
+      </c>
+      <c r="Z274" t="s" s="2">
         <v>1102</v>
       </c>
-      <c r="Z274" t="s" s="2">
-        <v>1103</v>
-      </c>
       <c r="AA274" t="s" s="2">
         <v>82</v>
       </c>
@@ -36699,7 +36696,7 @@
         <v>82</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>91</v>
@@ -36717,7 +36714,7 @@
         <v>82</v>
       </c>
       <c r="AL274" t="s" s="2">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="AM274" t="s" s="2">
         <v>109</v>
